--- a/Level3_LowerBody_Day2_V1+V2_TEST.xlsx
+++ b/Level3_LowerBody_Day2_V1+V2_TEST.xlsx
@@ -455,7 +455,7 @@
     <row r="2" ht="36" customHeight="1" s="13">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Every Level 3 Lower Body Day 2 test in one session — the same Test Day closes Version 1 and Version 2. PRESCRIPTION = the warm-up ramp, 2 sets per skill, then the official test at the exact standard, as many attempts as needed — hit it once to pass ✦. Film every pass and submit it to Skool.</t>
+          <t>Every test, one session. Warm up through the PRESCRIPTION (2 sets per test), then attempt the exact STANDARD — as many attempts as you need. Hit it once and it's passed ✦. Film that set and post it in Skool. Already passed a test on another Boss Test and posted it in Skool? It's done — no need to redo it. This Boss Test closes Version 1 and Version 2 of Day 2.</t>
         </is>
       </c>
     </row>
